--- a/sample-data/TB_AuditedFYEnd_FY25.xlsx
+++ b/sample-data/TB_AuditedFYEnd_FY25.xlsx
@@ -397,16 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Sample 01 High School — Trial Balance — Audited FY End (FY25)</v>
+        <v>Sample 01 High School — Audited Trial Balance</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>For the Year Ended June 30, 2025 — Audited</v>
+        <v>Fiscal Year FY25 — Audited Year-End — As of June 30, 2025</v>
       </c>
     </row>
     <row r="4">
@@ -428,308 +428,308 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>401</v>
+        <v>100</v>
       </c>
       <c r="B5" t="str">
-        <v>Tuition - net of discounts</v>
+        <v>Operating cash</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5">
-        <v>7820000</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5">
-        <v>-7820000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="B6" t="str">
-        <v>Registration fees</v>
+        <v>Tuition receivable</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6">
-        <v>138000</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6">
-        <v>-138000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>405</v>
+        <v>125</v>
       </c>
       <c r="B7" t="str">
-        <v>Application fees</v>
+        <v>Prepaid expenses</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7">
-        <v>41400</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7">
-        <v>-41400</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="B8" t="str">
-        <v>International program tuition</v>
+        <v>Restricted investments</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8">
-        <v>294400</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8">
-        <v>-294400</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>410</v>
+        <v>150</v>
       </c>
       <c r="B9" t="str">
-        <v>Textbook leasing income</v>
+        <v>Buildings &amp; improvements</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
-      <c r="D9">
-        <v>193200</v>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9">
-        <v>-193200</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>419</v>
+        <v>170</v>
       </c>
       <c r="B10" t="str">
-        <v>Other income</v>
+        <v>Accumulated depreciation</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
-      <c r="D10">
-        <v>34960</v>
+      <c r="D10" t="str">
+        <v/>
       </c>
       <c r="E10">
-        <v>-34960</v>
+        <v>-2500000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="B11" t="str">
-        <v>Student activity fees</v>
+        <v>Accounts payable &amp; accrued</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11">
-        <v>78200</v>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11">
-        <v>-78200</v>
+        <v>-700000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>450</v>
+        <v>230</v>
       </c>
       <c r="B12" t="str">
-        <v>Student club revenue</v>
+        <v>Deferred international tuition</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12">
-        <v>38640</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12">
-        <v>-38640</v>
+        <v>-200000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>453</v>
+        <v>260</v>
       </c>
       <c r="B13" t="str">
-        <v>Net gain (loss) on investments</v>
+        <v>Lease liability — noncurrent</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>119600</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13">
-        <v>-119600</v>
+        <v>-400000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="B14" t="str">
-        <v>Interest income</v>
+        <v>Tuition — net of discounts</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
-      <c r="D14">
-        <v>20240</v>
+      <c r="D14" t="str">
+        <v/>
       </c>
       <c r="E14">
-        <v>-20240</v>
+        <v>-9000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>475</v>
+        <v>407</v>
       </c>
       <c r="B15" t="str">
-        <v>Development - contributions</v>
+        <v>International program tuition</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15">
-        <v>515200</v>
+      <c r="D15" t="str">
+        <v/>
       </c>
       <c r="E15">
-        <v>-515200</v>
+        <v>-600000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>480</v>
+        <v>410</v>
       </c>
       <c r="B16" t="str">
-        <v>Annual fund support</v>
+        <v>Textbook leasing income</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>220800</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16">
-        <v>-220800</v>
+        <v>-120000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B17" t="str">
-        <v>Miscellaneous grant revenue</v>
+        <v>Student activity fees</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>13800</v>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17">
-        <v>-13800</v>
+        <v>-80000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="B18" t="str">
-        <v>Teacher salaries</v>
-      </c>
-      <c r="C18">
-        <v>3864000</v>
+        <v>Investment income</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18">
-        <v>3864000</v>
+        <v>-90000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="B19" t="str">
-        <v>Substitute salaries</v>
-      </c>
-      <c r="C19">
-        <v>87400</v>
+        <v>Interest income</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
       </c>
       <c r="D19" t="str">
         <v/>
       </c>
       <c r="E19">
-        <v>87400</v>
+        <v>-30000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="B20" t="str">
-        <v>Instructional supplies</v>
-      </c>
-      <c r="C20">
-        <v>165600</v>
+        <v>Contributions &amp; support</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20">
-        <v>165600</v>
+        <v>-400000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="B21" t="str">
-        <v>Classroom technology</v>
-      </c>
-      <c r="C21">
-        <v>110400</v>
+        <v>Instructional salaries</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21">
-        <v>110400</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B22" t="str">
-        <v>Library books and media</v>
-      </c>
-      <c r="C22">
-        <v>32200</v>
+        <v>Instructional supplies</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22">
-        <v>32200</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="23">
@@ -739,14 +739,14 @@
       <c r="B23" t="str">
         <v>Administrative salaries</v>
       </c>
-      <c r="C23">
-        <v>1058000</v>
+      <c r="C23" t="str">
+        <v/>
       </c>
       <c r="D23" t="str">
         <v/>
       </c>
       <c r="E23">
-        <v>1058000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="24">
@@ -754,616 +754,123 @@
         <v>620</v>
       </c>
       <c r="B24" t="str">
-        <v>Office expense</v>
-      </c>
-      <c r="C24">
-        <v>80960</v>
+        <v>Administrative costs</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24">
-        <v>80960</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="B25" t="str">
-        <v>Professional fees</v>
-      </c>
-      <c r="C25">
-        <v>128800</v>
+        <v>Facilities salaries</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
       </c>
       <c r="D25" t="str">
         <v/>
       </c>
       <c r="E25">
-        <v>128800</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="B26" t="str">
-        <v>Insurance</v>
-      </c>
-      <c r="C26">
-        <v>161000</v>
+        <v>Facilities &amp; maintenance</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26">
-        <v>161000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>700</v>
+        <v>865</v>
       </c>
       <c r="B27" t="str">
-        <v>Facilities salaries</v>
-      </c>
-      <c r="C27">
-        <v>349600</v>
+        <v>Depreciation expense</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27">
-        <v>349600</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>730</v>
+        <v>925</v>
       </c>
       <c r="B28" t="str">
-        <v>Utilities</v>
-      </c>
-      <c r="C28">
-        <v>220800</v>
+        <v>Transportation</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28">
-        <v>220800</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>740</v>
+        <v>935</v>
       </c>
       <c r="B29" t="str">
-        <v>Repairs and maintenance</v>
-      </c>
-      <c r="C29">
-        <v>151800</v>
+        <v>Food service</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
       </c>
       <c r="D29" t="str">
         <v/>
       </c>
       <c r="E29">
-        <v>151800</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="B30" t="str">
-        <v>Custodial supplies</v>
-      </c>
-      <c r="C30">
-        <v>44160</v>
+        <v>Athletics</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
       </c>
       <c r="D30" t="str">
         <v/>
       </c>
       <c r="E30">
-        <v>44160</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>820</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Equipment expense</v>
-      </c>
-      <c r="C31">
-        <v>55200</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31">
-        <v>55200</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>865</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Depreciation expense</v>
-      </c>
-      <c r="C32">
-        <v>386400</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32">
-        <v>386400</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>880</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Interest expense</v>
-      </c>
-      <c r="C33">
-        <v>32200</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33">
-        <v>32200</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>925</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Pupil transportation</v>
-      </c>
-      <c r="C34">
-        <v>193200</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34">
-        <v>193200</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>935</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Food service costs</v>
-      </c>
-      <c r="C35">
-        <v>151800</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35">
-        <v>151800</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>950</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Athletics - operations</v>
-      </c>
-      <c r="C36">
-        <v>133400</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36">
-        <v>133400</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>952</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Athletics - equipment</v>
-      </c>
-      <c r="C37">
-        <v>34960</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37">
-        <v>34960</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>988</v>
-      </c>
-      <c r="B38" t="str">
-        <v>International program expense</v>
-      </c>
-      <c r="C38">
-        <v>165600</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38">
-        <v>165600</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>960</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Restricted program expenditures</v>
-      </c>
-      <c r="C39">
-        <v>82800</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39">
-        <v>82800</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>100</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Operating cash</v>
-      </c>
-      <c r="C40">
-        <v>1125000</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40">
-        <v>1125000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>101</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Payroll cash</v>
-      </c>
-      <c r="C41">
-        <v>162000</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41">
-        <v>162000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>110</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Region endowment savings</v>
-      </c>
-      <c r="C42">
-        <v>306000</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42">
-        <v>306000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>112</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Student club cash</v>
-      </c>
-      <c r="C43">
-        <v>37800</v>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43">
-        <v>37800</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>120</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Tuition receivable</v>
-      </c>
-      <c r="C44">
-        <v>432000</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44">
-        <v>432000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>120</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Prepaid TMS Fees</v>
-      </c>
-      <c r="C45">
-        <v>23400</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45">
-        <v>23400</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>120</v>
-      </c>
-      <c r="B46" t="str">
-        <v>TMS Suspense</v>
-      </c>
-      <c r="C46">
-        <v>10800</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>120</v>
-      </c>
-      <c r="B47" t="str">
-        <v>TMS Payment at Institution</v>
-      </c>
-      <c r="C47">
-        <v>7200</v>
-      </c>
-      <c r="D47" t="str">
-        <v/>
-      </c>
-      <c r="E47">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>125</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Prepaid insurance</v>
-      </c>
-      <c r="C48">
-        <v>85500</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48">
-        <v>85500</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>135</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Restricted investments</v>
-      </c>
-      <c r="C49">
-        <v>1620000</v>
-      </c>
-      <c r="D49" t="str">
-        <v/>
-      </c>
-      <c r="E49">
-        <v>1620000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>150</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Buildings</v>
-      </c>
-      <c r="C50">
-        <v>11250000</v>
-      </c>
-      <c r="D50" t="str">
-        <v/>
-      </c>
-      <c r="E50">
-        <v>11250000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>151</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Land improvements</v>
-      </c>
-      <c r="C51">
-        <v>765000</v>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51">
-        <v>765000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>165</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Vehicles</v>
-      </c>
-      <c r="C52">
-        <v>288000</v>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52">
-        <v>288000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>160</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Right-to-use lease asset</v>
-      </c>
-      <c r="C53">
-        <v>486000</v>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53">
-        <v>486000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>170</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Accumulated depreciation</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54">
-        <v>4680000</v>
-      </c>
-      <c r="E54">
-        <v>-4680000</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>200</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Accounts payable and accrued</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55">
-        <v>378000</v>
-      </c>
-      <c r="E55">
-        <v>-378000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>200</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Lease obligation - current portion</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56">
-        <v>162000</v>
-      </c>
-      <c r="E56">
-        <v>-162000</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>230</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Deferred international program fees</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57">
-        <v>135000</v>
-      </c>
-      <c r="E57">
-        <v>-135000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>240</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Due to student clubs</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58">
-        <v>37800</v>
-      </c>
-      <c r="E58">
-        <v>-37800</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>260</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Lease obligation - noncurrent</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59">
-        <v>549000</v>
-      </c>
-      <c r="E59">
-        <v>-549000</v>
+        <v>200000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E30"/>
   </ignoredErrors>
 </worksheet>
 </file>